--- a/xls2rdf-lib/src/test/resources/excel/suite/_45_asList/input.xlsx
+++ b/xls2rdf-lib/src/test/resources/excel/suite/_45_asList/input.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
@@ -9,11 +9,14 @@
     <sheet name="QuantityValue" sheetId="1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Graph URI</t>
   </si>
@@ -36,6 +39,9 @@
     <t>ex:value(asList="true")</t>
   </si>
   <si>
+    <t xml:space="preserve">ex:value2(separator=";" asList="true")</t>
+  </si>
+  <si>
     <t>ex:TEST</t>
   </si>
   <si>
@@ -44,13 +50,19 @@
   <si>
     <t>ex:2</t>
   </si>
+  <si>
+    <t>ex:TEST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex:1; ex:2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="160" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -546,17 +558,17 @@
     <xf fontId="16" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="160" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1138,7 +1150,6 @@
     <row r="3">
       <c r="C3" s="2"/>
     </row>
-    <row r="4" ht="14.25"/>
     <row r="5" s="1" customFormat="1">
       <c r="A5" s="4" t="s">
         <v>5</v>
@@ -1146,65 +1157,35 @@
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>9</v>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" ht="14.25"/>
-    <row r="9" ht="14.25"/>
-    <row r="10" ht="14.25"/>
-    <row r="11" ht="14.25"/>
-    <row r="12" ht="14.25"/>
-    <row r="13" ht="14.25"/>
-    <row r="14" ht="14.25"/>
-    <row r="15" ht="14.25"/>
-    <row r="16" ht="14.25"/>
-    <row r="17" ht="14.25"/>
-    <row r="18" ht="14.25"/>
-    <row r="19" ht="14.25"/>
-    <row r="20" ht="14.25"/>
-    <row r="21" ht="14.25"/>
-    <row r="22" ht="14.25"/>
-    <row r="23" ht="14.25"/>
-    <row r="24" ht="14.25"/>
-    <row r="25" ht="14.25"/>
-    <row r="26" ht="14.25"/>
-    <row r="27" ht="14.25"/>
-    <row r="28" ht="14.25"/>
-    <row r="29" ht="14.25"/>
-    <row r="30" ht="14.25"/>
-    <row r="31" ht="14.25"/>
-    <row r="32" ht="14.25"/>
-    <row r="33" ht="14.25"/>
-    <row r="34" ht="14.25"/>
-    <row r="35" ht="14.25"/>
-    <row r="36" ht="14.25"/>
-    <row r="37" ht="14.25"/>
-    <row r="38" ht="14.25"/>
-    <row r="39" ht="14.25"/>
-    <row r="40" ht="14.25"/>
-    <row r="41" ht="14.25"/>
-    <row r="42" ht="14.25"/>
-    <row r="43" ht="14.25"/>
-    <row r="44" ht="14.25"/>
-    <row r="45" ht="14.25"/>
-    <row r="46" ht="14.25"/>
-    <row r="47" ht="14.25"/>
+    <row r="8" ht="14.25">
+      <c r="A8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B1"/>
@@ -1385,9 +1366,7 @@
         <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
         <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
           <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
+            <xsd:documentation>This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.</xsd:documentation>
           </xsd:annotation>
         </xsd:element>
         <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1471,18 +1450,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA1FA1F-0E69-410D-8DC2-248841F3EE28}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="BEA1FA1F-0E69-410D-8DC2-248841F3EE28">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="21f64c02-1f20-443d-801b-ae17df5c4a0a"/>
     <ds:schemaRef ds:uri="bf3f9575-65b8-4549-b389-33a18b8943d7"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43680BD2-8DC0-4F1D-A4CD-B5AFA7401544}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="43680BD2-8DC0-4F1D-A4CD-B5AFA7401544">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1496,12 +1476,13 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F32C29-5119-4529-9D4B-832730A3AB27}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="A1F32C29-5119-4529-9D4B-832730A3AB27">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
